--- a/data/output/evaluasi_81.xlsx
+++ b/data/output/evaluasi_81.xlsx
@@ -8,8 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="8100" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="8172" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="8107" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="8105" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="8101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="8102" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="8171" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="8172" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="8106" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8108" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8109" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="8107" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="8103" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="8104" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,16 +486,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.297075361672912</v>
+        <v>25.83152600572591</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pkp_q1-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -501,20 +510,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.23997915824771</v>
+        <v>17.59564514203622</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -529,20 +538,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.064240843192239</v>
+        <v>19.07377046631386</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -561,16 +570,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.172848054053544</v>
+        <v>9.881370002385101</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_pkp_q1-25</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -585,20 +594,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.46863721492631</v>
+        <v>-3.400336763530493</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -617,16 +626,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.480040560334673</v>
+        <v>25.22391910653479</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -645,16 +654,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.252541652627399</v>
+        <v>5.390619404092842</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pdrb_q1-25 vs implisit_q-to-q_pdrb_q1-25.1</t>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -673,16 +682,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.383717457418646</v>
+        <v>11.27130207463436</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -697,20 +706,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.158881835703934</v>
+        <v>-7.654930919318105</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -725,20 +734,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.268324555103396</v>
+        <v>0.174654703415879</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
         </is>
       </c>
     </row>
@@ -757,16 +766,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2.061099987577153</v>
+        <v>5.390619404092842</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -785,16 +794,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.9669536266829518</v>
+        <v>11.27130207463436</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pdrb_q1-25 vs implisit_y-on-y_pdrb_q1-25.1</t>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -809,20 +818,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.553090678535434</v>
+        <v>0.05216323156336705</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pdrb_q2-25 vs implisit_y-on-y_pdrb_q2-25.1</t>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -841,16 +850,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.8916239196462796</v>
+        <v>-3.939663319037721</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -869,16 +878,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.6308020199240267</v>
+        <v>-1.858808299137059</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+          <t>implisit_y-on-y_pkrt_q1-25 vs implisit_y-on-y_pkrt_q1-25.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -893,20 +902,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.7185795370555504</v>
+        <v>-2.239673061933045</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+          <t>implisit_y-on-y_pkrt_q2-25 vs implisit_y-on-y_pkrt_q2-25.1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -921,20 +930,410 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.7120336950084935</v>
+        <v>-0.09469007952730277</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
+          <t>implisit_y-on-y_pkrt_q3-25 vs implisit_y-on-y_pkrt_q3-25.1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>81</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Maluku</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4.110355564121862</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2971605985161569</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.354639697252579</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.02804303359719876</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.7803134713946989</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.1143566041747015</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.161898775542872</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.227002814295007</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08582529632085129</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -949,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,11 +1385,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8172</v>
+        <v>8105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Tual</t>
+          <t>Kabupaten Kepulauan Aru</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -999,464 +1398,184 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>453419.9397251881</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pdrb_q1-25_ril vs adhb_pdrb_q1-25_rev</t>
+          <t>distribusi_pkrt_q1-25_ril vs distribusi_pkrt_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-5 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8172</v>
+        <v>8105</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Tual</t>
+          <t>Kabupaten Kepulauan Aru</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>262787.6667639738</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_pkrt_q1-25_ril vs adhb_pkrt_q1-25_rev</t>
+          <t>distribusi_pkrt_q2-25_ril vs distribusi_pkrt_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-5 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8172</v>
+        <v>8105</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Tual</t>
+          <t>Kabupaten Kepulauan Aru</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11269.6479776884</v>
+        <v>0.2759715726872729</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhb_pklnprt_q1-25_ril vs adhb_pklnprt_q1-25_rev</t>
+          <t>c-to-c_pmtb_q2-25_ril vs c-to-c_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8172</v>
+        <v>8105</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kota Tual</t>
+          <t>Kabupaten Kepulauan Aru</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>88707.83575426</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhb_pkp_q1-25_ril vs adhb_pkp_q1-25_rev</t>
+          <t>implisit_y-on-y_pkrt_q2-25_ril vs implisit_y-on-y_pkrt_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8172</v>
+        <v>8105</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kota Tual</t>
+          <t>Kabupaten Kepulauan Aru</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>140711.4727296531</v>
+        <v>-0.02513684350008738</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhb_pmtb_q1-25_ril vs adhb_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8172</v>
+        <v>8105</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kota Tual</t>
+          <t>Kabupaten Kepulauan Aru</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3551.70169003186</v>
+        <v>-6.582822309336243</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8172</v>
+        <v>8105</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kota Tual</t>
+          <t>Kabupaten Kepulauan Aru</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-53608.3851904191</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-46.72329120041223</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pdrb_q1-25_ril vs implisit_q-to-q_pdrb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-52.31797279595665</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>-45.41866327478014</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>-45.83848998606179</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>-42.41865586230743</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>-46.18654661186816</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pdrb_q1-25_ril vs implisit_y-on-y_pdrb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>-51.95117915772782</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>-45.40789749644021</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>-45.52236143829367</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>8172</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Kota Tual</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>-41.86598379135474</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1508,67 +1627,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8107</v>
+        <v>8101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Seram Bagian Timur</t>
+          <t>Kabupaten Kepulauan Tanimbar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-477664.5190050841</v>
+        <v>29.03959144607906</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8107</v>
+        <v>8101</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Seram Bagian Timur</t>
+          <t>Kabupaten Kepulauan Tanimbar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6446035255666378</v>
+        <v>-0.07202119586040048</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8107</v>
+        <v>8101</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Seram Bagian Timur</t>
+          <t>Kabupaten Kepulauan Tanimbar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1577,72 +1696,1244 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-47.73033948488087</v>
+        <v>-0.04434207222662304</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8107</v>
+        <v>8101</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Seram Bagian Timur</t>
+          <t>Kabupaten Kepulauan Tanimbar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.009727902018364983</v>
+        <v>-0.02362794809132268</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8107</v>
+        <v>8101</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Seram Bagian Timur</t>
+          <t>Kabupaten Kepulauan Tanimbar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.162208705571668</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>27.74795486770151</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>6.528267906857486</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.06773281167711979</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25_ril vs y-on-y_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.528267906857486</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
       <c r="D6" t="n">
-        <v>-76.01432620061901</v>
+        <v>-0.02396555361267421</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>sog_y-on-y_pmtb_q2-25_ril vs sog_y-on-y_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.335684409714198</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2270789003122632</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.270854202447294</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.199899898496546</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.06424382799506902</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>24.86875436163556</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12.01930176427802</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.01930176427802</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.06070402802939349</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.1019723166223</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.1474187789488888</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.09733580000133475</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.07763071392475529</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2518661696910214</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.263607378668775</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.06202026588823749</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3071121947717935</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>33.38242136479703</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.332657101579797</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1076215476171967</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.9688823056452713</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.09197007296926571</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.627665798839608</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.454921051976497</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.840447010112463</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.765485253973077</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.6011016812374356</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_81.xlsx
+++ b/data/output/evaluasi_81.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
